--- a/assets/Equipment.xlsx
+++ b/assets/Equipment.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,12 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,22 +85,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,17 +461,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -485,372 +481,1012 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Gain 1 Energy immediately (spendable this Main Phase).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Gain 10 Energy immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Chaos Emerald</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>chaos_emerald</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Leader gains +2 Damage until end of this turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Leader gains +20 Damage until end of this turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Elemental Shield</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>elemental_shield</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-20 to the next instance of damage you receive (applies once, then clears).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Heat Barrier</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>heat_barrier</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Heal your Leader for 20 HP. Cannot exceed max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Dragon's Eye</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>dragons_eye</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Look at the top 3 cards of your deck. Put 1 into your hand; return the rest on top in any order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Power Glove</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>power_glove</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Your Leader deals +30 Damage this turn only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Speed Shoes</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>speed_shoes</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Gain 30 Energy immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Extreme Gear</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>extreme_gear</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Discard up to 3 cards from your hand — gain 10 Energy per card discarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Green Hill Zone</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>green_hill_zone</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>While active: both players draw 1 extra card during Draw Phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Midnight Carnival</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>midnight_carnival</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>While active: KO'd bench units deal 0 penalty damage to their controller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Radical Highway</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>radical_highway</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>While active: each player gains 10 extra energy at the start of their turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Master Emerald</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>master_emerald</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>This turn: all bench unit actives cost 0 and do not exhaust. Cleared in End Phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Polaris Pact</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>polaris_pact</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>This turn: all bench unit actives cost 0 and do not exhaust. Cleared in End Phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Green Hill Zone</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>If a friendly support died last turn: both players shuffle their hands into their decks. You draw 5, opponent draws 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Super Form</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>super_form</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Double your current energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Calling Card</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>calling_card</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Your opponent discards a card from their hand at random.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Treasure (Distorted Desire)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>treasure_distorted_desire</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Your Leader gains +20 Damage this turn. If your opponent has 3 or fewer cards in hand, gain +40 instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LeBlanc Coffee</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>leblanc_coffee</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Heal your Leader for 20 HP. Then you may discard 1 card and draw 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Third Eye</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>third_eye</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Look at the top 3 cards of your deck. Take 1 into hand. Your opponent discards a card from their hand at random.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Phantom Thief Tools</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>phantom_thief_tools</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Gain 20 Energy for this turn. If your opponent has more cards than you, gain 30 instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Metaverse Navigator</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>metaverse_navigator</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Both players discard their hand and draw that many cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Guard Persona</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>guard_persona</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Prevent ALL damage to yourself during your opponent's next turn. Afterward, your opponent discards 1 card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>All-Out Attack</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>all_out_attack</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Your Leader deals +30 Damage this turn. If your opponent has 2 or fewer cards in hand, deal +50 instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Shibuya Crossing</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>shibuya_crossing</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>While active: both players draw 1 extra card during Draw Phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Elemental Shield</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+      <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Prevent ALL damage to yourself during your opponent's next turn (including KO penalty). Shield clears after absorbing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Heat Barrier</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>While active: both players draw 1 extra card during Draw Phase. Whenever your opponent draws outside Draw Phase, they discard 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Mementos Depths</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>mementos_depths</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>While active: when a support unit is KO'd, its controller discards 1 card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Palace Infiltration Route</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>palace_infiltration_route</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Heal your Leader for 2 HP. Cannot exceed max HP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Dragon's Eye</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the top 3 cards of your deck. Put 1 into your hand; return the rest on top in any order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Power Glove</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Your Leader deals +3 Damage this turn only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Midnight Carnival</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>While active: when a bench unit is KO'd, its controller takes 0 penalty damage instead of 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Polaris Pact</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>While active: each player gains 10 extra energy at the start of their turn and takes 10 damage to their leader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Holy Grail</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>holy_grail</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>This turn all support unit actives cost 0 and do not exhaust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Contract of Rebellion</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>contract_of_rebellion</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Both players draw until they have 6 cards. Then your opponent discards 2 cards and cannot draw outside Draw Phase until your next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Arsène Unleashed</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>arsene_unleashed</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Both players draw until they have 6 cards in hand. Then your opponent discards 1 card of their choice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Speed Shoes</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Gain 3 Energy immediately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Extreme Gear</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Discard any number of cards from your hand — gain 1 Energy for each card discarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Radical Highway</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>While active: each player gains 1 extra energy at the start of their turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Super Form</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
+      <c r="E29" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Genesis</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Double your current energy.</t>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Set a leader's HP to half of their original max HP (rounded down).</t>
         </is>
       </c>
     </row>

--- a/assets/Equipment.xlsx
+++ b/assets/Equipment.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sonic IP Cards" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persona 5 IP Cards" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sonic IP Cards'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Persona 5 IP Cards'!$A$1:$G$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,176 +21,298 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00E8F0FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0000CC44"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC44FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF2244"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007AFFA0"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF88DD"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF2244"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
-      <patternFill patternType="solid"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="000066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="000D2040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="001E1E1E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D2A10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A0A30"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
-      <bottom>
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="FF000000"/>
-      </diagonal>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -479,397 +604,523 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000D2040"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Copy Limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Gain 1 Energy immediately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Gain 1 Energy immediately (can be spent this same Main Phase).</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Speed Shoes</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Gain 3 Energy immediately.</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="G3" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Extreme Gear</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Discard up to 3 cards from your hand — gain 1 Energy per card discarded.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="G4" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Chili Dog</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Heal your Leader for 20 HP. Cannot exceed max HP.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="G5" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Elemental Shield</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>-20 to the next instance of damage you receive (applies once, then clears).</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Chaos Emerald</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Leader gains +20 Damage until end of this turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Leader gains +20 Damage until end of this turn. Cleared in End Phase.</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dragon's Eye</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Look at the top 3 cards of your deck. Put 1 into your hand; return the rest on top in any order.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Power Glove</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Your Leader deals +30 Damage this turn only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Your Leader deals +30 Damage this turn only. Cleared in End Phase.</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Green Hill Zone</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>While active: both players draw 1 extra card during Draw Phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>While active: both players draw 1 extra card during Draw Phase. Replaces previous Stage when played.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Radical Highway</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>While active: each player gains 1 extra energy at the start of their turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>While active: each player gains 1 extra energy at the start of the active player's turn.</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Midnight Carnival</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>While active: KO'd bench units deal 0 penalty damage to their controller.</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="G12" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Master Emerald</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>This turn: all bench unit actives cost 0 and do not exhaust. Cleared in End Phase.</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="G13" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Polaris Pact</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>If a friendly support unit died last turn: both players shuffle their hands into their decks. You draw 5, opponent draws 2.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G14" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Super Form</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Double your current energy.</t>
         </is>
       </c>
+      <c r="G15" s="18" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -877,397 +1128,523 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A0D20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Copy Limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Calling Card</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your opponent discards a card from their hand at random. </t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Your opponent discards a card from their hand at random.</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Treasure (Distorted Desire)</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Your Leader gains +2 Damage this turn. If your opponent has 3 or fewer cards in hand, gain +4 instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Leader gains +20 Damage this turn. If opponent has ≤3 cards in hand, +40 instead.</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>LeBlanc Coffee</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Heal your Leader for 20 HP. Then you may discard 1 card and draw 1.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Third Eye</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Look at top 3 deck cards — take 1 into hand. Opponent discards 1 at random.</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Phantom Thief Tools</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Gain 2 Energy. If opponent has more cards than you, gain 3 instead.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Metaverse Navigator</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Both players discard their hand and draw that many cards.</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Guard Persona</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Prevent ALL damage to yourself during opponent's next turn. Afterward, opponent discards 1 card.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>All-Out Attack</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Leader deals +30 Damage this turn. If opponent has ≤2 cards in hand, +50 instead.</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Shibuya Crossing</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>While active: both players draw 1 extra card each Draw Phase. Whenever opponent draws outside Draw Phase, they discard 1.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Mementos Depths</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>While active: when a support unit is KO'd, its controller discards 1 card.</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Palace Infiltration Route</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>While active: each player gains 1 extra energy at the start of the active player's turn and takes 10 damage to their leader.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Holy Grail</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This turn all support unit actives cost 0 and do not exhaust. </t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Shibuya Crossing</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>This turn: all bench unit actives cost 0 and do not exhaust. Cleared in End Phase.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Both players draw 1 extra card during Draw Phase. Whenever your opponent draws outside Draw Phase, they discard 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Guard Persona</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Prevent ALL damage to yourself during your opponent's next turn. Afterward, your opponent discards 1 card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Leblanc Coffee</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Contract of Rebellion</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Both players draw until they have 6 cards. Opponent discards 2 and cannot draw outside Draw Phase until your next turn.</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Heal your Leader for 2 HP. Then you may discard 1 card and draw 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Third Eye</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Look at the top 3 cards of your deck. Take 1 into hand. Your opponent discards a card from their hand at random. </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>All-Out Attack</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Your Leader deals +3 Damage this turn. If your opponent has 2 or fewer cards in hand, deal +5 instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Mementos Depths</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>While active: when a support unit is KO’d, its controller discards 1 card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Contract of Rebellion</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Arsène Unleashed</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Genesis</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Both players draw until they have 6 cards. Then your opponent discards 2 cards and cannot draw outside Draw Phase until your next turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Phantom Thief Tools</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Set any leader's HP to half of their original max HP (rounded down). Choose the target.</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Phantom Thieves</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Gain 2 Energy for this turn. If your opponent has more cards than you, gain 3 instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Metaverse Navigator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Phantom Thieves</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both players discard their hand and draw that many cards. </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Palace Infiltration Route</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Phantom Thieves</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>While active: Each player gains 1 extra energy at the start of their turn and takes 1 damage to their leader.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Arsène Unleashed</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Genesis</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Phantom Thieves</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Set a leader cards HP to half of the original number. </t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>